--- a/spatialnames.xlsx
+++ b/spatialnames.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NoOfElements</t>
+          <t>ClusterSize</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AtypicalNoOfElements</t>
+          <t>AtypicalClusterSize</t>
         </is>
       </c>
     </row>
